--- a/tests/fixtures/07_timesheet/07_timesheet_pattern-from-claude.xlsx
+++ b/tests/fixtures/07_timesheet/07_timesheet_pattern-from-claude.xlsx
@@ -736,7 +736,7 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>number</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
